--- a/artfynd/A 35519-2026 artfynd.xlsx
+++ b/artfynd/A 35519-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91841171</v>
+        <v>137504226</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>96647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Galberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436090</v>
+        <v>436228</v>
       </c>
       <c r="R2" t="n">
-        <v>6966911</v>
+        <v>6967074</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +765,31 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91841171</t>
+          <t>https://artportalen.se/Sighting/137504226</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91953959</v>
+        <v>137504215</v>
       </c>
       <c r="B3" t="n">
-        <v>104628</v>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Galberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436232</v>
+        <v>436152</v>
       </c>
       <c r="R3" t="n">
-        <v>6966914</v>
+        <v>6966867</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,40 +867,35 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Brunjord. Kalktallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91953959</t>
+          <t>https://artportalen.se/Sighting/137504215</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>91953950</v>
+        <v>137504219</v>
       </c>
       <c r="B4" t="n">
-        <v>99038</v>
+        <v>93157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,33 +903,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223597</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jämtlands län, Jmt</t>
+          <t>Galberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436241</v>
+        <v>436244</v>
       </c>
       <c r="R4" t="n">
-        <v>6967072</v>
+        <v>6967037</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2019-06-01</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2019-10-31</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,20 +977,657 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504219</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>91841171</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>436090</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6966911</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Via Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91841171</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137504212</v>
+      </c>
+      <c r="B6" t="n">
+        <v>108213</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Galberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>436240</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6967193</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504212</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>91953959</v>
+      </c>
+      <c r="B7" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>436232</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6966914</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Brunjord. Kalktallskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91953959</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137504218</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101049</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Galberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>436217</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6967191</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504218</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137504220</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101049</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222584</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bergsslok</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Galberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>436230</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6967074</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>LstZ naturskyddsfunktionens naturvärdesinventering 2026</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137504220</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>91953950</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jämtlands län, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>436241</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6967072</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åsarne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-06-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-10-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/91953950</t>
         </is>
@@ -1002,6 +1638,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35519-2026 artfynd.xlsx
+++ b/artfynd/A 35519-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137504226</v>
       </c>
       <c r="B2" t="n">
-        <v>96647</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137504215</v>
       </c>
       <c r="B3" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137504219</v>
       </c>
       <c r="B4" t="n">
-        <v>93157</v>
+        <v>93160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137504212</v>
       </c>
       <c r="B6" t="n">
-        <v>108213</v>
+        <v>108217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         <v>137504218</v>
       </c>
       <c r="B8" t="n">
-        <v>101049</v>
+        <v>101052</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>137504220</v>
       </c>
       <c r="B9" t="n">
-        <v>101049</v>
+        <v>101052</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
